--- a/DocBusinessThienAn/BaoCao/KPI/2026.09_KPI_DatHoangQuy.xlsx
+++ b/DocBusinessThienAn/BaoCao/KPI/2026.09_KPI_DatHoangQuy.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30420" windowHeight="15760"/>
+    <workbookView windowWidth="30420" windowHeight="16560" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="01. Tổng task" sheetId="1" r:id="rId1"/>
@@ -195,7 +195,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="336">
   <si>
     <t>BÁO CÁO TỔNG HỢP CÔNG VIỆC TRONG THÁNG</t>
   </si>
@@ -1103,7 +1103,18 @@
     <t>Ngắn hạn (1-2 năm)</t>
   </si>
   <si>
+    <t>- Nắm bắt luồng dữ liệu và nghiệp vụ tổng thể của toàn hệ thống ITS.
+- Độc lập phụ trách thiết kế, triển khai và tối ưu các module nghiệp vụ được giao.
+- Nghiên cứu, ứng dụng các công nghệ và giải pháp mới vào sản phẩm.</t>
+  </si>
+  <si>
     <t>Dài hạn (3-5 năm)</t>
+  </si>
+  <si>
+    <t>- Đảm nhiệm vai trò Tech Lead, chịu trách nhiệm về kiến trúc kỹ thuật và chất lượng bàn giao của dự án.
+- Làm cầu nối kỹ thuật giữa khách hàng/ban quản lý và đội ngũ phát triển: làm rõ yêu cầu, lập kế hoạch, phân bổ task và báo cáo định kỳ.
+- Thiết lập tiêu chuẩn kỹ thuật, thực hiện review code và quản lý rủi ro kỹ thuật.
+- Xây dựng tài liệu kỹ thuật, hướng dẫn và đào tạo đội ngũ kế cận cho dự án.</t>
   </si>
   <si>
     <t>CHỮ KÝ NHÂN VIÊN</t>
@@ -1615,7 +1626,7 @@
     <numFmt numFmtId="180" formatCode="0.0"/>
     <numFmt numFmtId="181" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="69">
+  <fonts count="68">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1785,13 +1796,6 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color rgb="FFFFC000"/>
-      <name val="Segoe UI Semibold"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF166534"/>
       <name val="Segoe UI"/>
@@ -1802,6 +1806,13 @@
       <sz val="10"/>
       <color rgb="FFF48F02"/>
       <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFFC000"/>
+      <name val="Segoe UI Semibold"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1905,11 +1916,6 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Carlito"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -2048,6 +2054,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <i/>
+      <sz val="10"/>
+      <color theme="0" tint="-0.0499893185216834"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color theme="0" tint="-0.0499893185216834"/>
@@ -2064,14 +2085,6 @@
     <font>
       <b/>
       <i/>
-      <sz val="10"/>
-      <color theme="0" tint="-0.0499893185216834"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
       <sz val="11"/>
       <color theme="0" tint="-0.0499893185216834"/>
       <name val="Segoe UI"/>
@@ -2082,13 +2095,6 @@
       <sz val="11"/>
       <color rgb="FF2D3748"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="14"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2951,19 +2957,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF8DB4E2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD5DEE8"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD5DEE8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFD5DEE8"/>
       </left>
@@ -3197,6 +3190,19 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF8DB4E2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD5DEE8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD5DEE8"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3758,7 +3764,7 @@
     <xf numFmtId="177" fontId="43" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="44" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="178" fontId="43" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3766,130 +3772,130 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="32" borderId="98" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="32" borderId="98" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="99" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="99" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="99" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="100" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="100" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="51" fillId="33" borderId="101" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="33" borderId="101" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="52" fillId="34" borderId="102" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="34" borderId="102" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="53" fillId="34" borderId="101" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="34" borderId="101" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="54" fillId="35" borderId="103" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="35" borderId="103" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="104" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="104" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="105" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="105" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="57" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="58" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="59" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="60" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="61" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="61" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="60" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="60" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="61" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="61" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="60" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="60" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="61" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="61" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="60" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="60" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="61" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="61" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="60" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="60" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="61" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="61" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="60" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="60" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="61" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="61" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="60" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4187,22 +4193,19 @@
     <xf numFmtId="0" fontId="25" fillId="26" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="26" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="26" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4263,11 +4266,11 @@
     <xf numFmtId="2" fontId="7" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="27" fillId="28" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="26" fillId="28" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4277,12 +4280,12 @@
     <xf numFmtId="0" fontId="24" fillId="25" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4307,7 +4310,7 @@
     <xf numFmtId="9" fontId="23" fillId="27" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="28" fillId="27" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="27" fillId="27" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4334,31 +4337,31 @@
     <xf numFmtId="9" fontId="23" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="28" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="27" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="27" fillId="28" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="26" fillId="28" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="23" fillId="27" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4382,41 +4385,44 @@
     <xf numFmtId="2" fontId="23" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="27" fillId="28" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="26" fillId="28" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="27" fillId="28" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="26" fillId="28" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="14" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4424,13 +4430,10 @@
     <xf numFmtId="0" fontId="11" fillId="14" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="9" fillId="13" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4443,13 +4446,13 @@
     <xf numFmtId="0" fontId="23" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="27" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4465,13 +4468,16 @@
     <xf numFmtId="0" fontId="23" fillId="27" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="30" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="30" fillId="27" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4483,10 +4489,10 @@
     <xf numFmtId="0" fontId="23" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4498,7 +4504,7 @@
     <xf numFmtId="0" fontId="32" fillId="28" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="28" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="28" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="28" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4627,7 +4633,7 @@
     <xf numFmtId="9" fontId="23" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="23" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="23" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="39" fillId="0" borderId="79" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4636,7 +4642,7 @@
     <xf numFmtId="0" fontId="23" fillId="31" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4714,22 +4720,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="91" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="91" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="92" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="92" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="27" fillId="28" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="26" fillId="28" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="27" fillId="28" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="26" fillId="28" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4745,10 +4751,10 @@
     <xf numFmtId="1" fontId="7" fillId="13" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="13" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="13" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="13" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="13" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="13" borderId="95" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4760,7 +4766,7 @@
     <xf numFmtId="1" fontId="8" fillId="13" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="13" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="13" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="13" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7872,15 +7878,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>621195</xdr:colOff>
+      <xdr:colOff>532765</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>49696</xdr:rowOff>
+      <xdr:rowOff>36830</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>21535</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>651925</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>285916</xdr:rowOff>
+      <xdr:rowOff>273050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7906,7 +7912,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5405120" y="22157055"/>
+          <a:off x="5316855" y="22144355"/>
           <a:ext cx="118745" cy="236220"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7919,15 +7925,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>414130</xdr:colOff>
+      <xdr:colOff>139700</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>41414</xdr:rowOff>
+      <xdr:rowOff>53975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>638920</xdr:colOff>
+      <xdr:colOff>364490</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>270014</xdr:rowOff>
+      <xdr:rowOff>282575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7953,7 +7959,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5198110" y="20845780"/>
+          <a:off x="4923790" y="20858480"/>
           <a:ext cx="224790" cy="228600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7966,15 +7972,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>745435</xdr:colOff>
+      <xdr:colOff>556260</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>33131</xdr:rowOff>
+      <xdr:rowOff>33020</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>141965</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>698225</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>257921</xdr:rowOff>
+      <xdr:rowOff>257810</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -8000,7 +8006,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5502910" y="23795990"/>
+          <a:off x="5340350" y="23795990"/>
           <a:ext cx="141605" cy="224790"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -10475,7 +10481,7 @@
         <v>(41)</v>
       </c>
     </row>
-    <row r="13" s="232" customFormat="1" ht="87" spans="1:41">
+    <row r="13" s="232" customFormat="1" ht="87" customHeight="1" spans="1:41">
       <c r="A13" s="267">
         <v>1</v>
       </c>
@@ -10618,7 +10624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" s="232" customFormat="1" ht="101.75" spans="1:41">
+    <row r="14" s="232" customFormat="1" ht="101.75" customHeight="1" spans="1:41">
       <c r="A14" s="277">
         <v>2</v>
       </c>
@@ -11264,20 +11270,20 @@
         <f>SUM(I13:I19)</f>
         <v>8</v>
       </c>
-      <c r="J20" s="174"/>
-      <c r="K20" s="174"/>
-      <c r="L20" s="174"/>
-      <c r="M20" s="174"/>
-      <c r="N20" s="174"/>
-      <c r="O20" s="174"/>
-      <c r="P20" s="174"/>
-      <c r="Q20" s="174"/>
-      <c r="R20" s="174"/>
-      <c r="S20" s="174"/>
-      <c r="T20" s="174"/>
-      <c r="U20" s="174"/>
-      <c r="V20" s="174"/>
-      <c r="W20" s="174"/>
+      <c r="J20" s="173"/>
+      <c r="K20" s="173"/>
+      <c r="L20" s="173"/>
+      <c r="M20" s="173"/>
+      <c r="N20" s="173"/>
+      <c r="O20" s="173"/>
+      <c r="P20" s="173"/>
+      <c r="Q20" s="173"/>
+      <c r="R20" s="173"/>
+      <c r="S20" s="173"/>
+      <c r="T20" s="173"/>
+      <c r="U20" s="173"/>
+      <c r="V20" s="173"/>
+      <c r="W20" s="173"/>
       <c r="X20" s="296">
         <f>IFERROR(SUM(AH13:AH19)/SUM(AL13:AL19),0)</f>
         <v>100</v>
@@ -11376,16 +11382,16 @@
       <c r="B27" s="25"/>
       <c r="C27" s="26"/>
       <c r="D27" s="299"/>
-      <c r="E27" s="185" t="s">
+      <c r="E27" s="184" t="s">
         <v>76</v>
       </c>
-      <c r="F27" s="186"/>
-      <c r="G27" s="186"/>
-      <c r="H27" s="186"/>
-      <c r="I27" s="186"/>
-      <c r="J27" s="186"/>
-      <c r="K27" s="186"/>
-      <c r="L27" s="187"/>
+      <c r="F27" s="185"/>
+      <c r="G27" s="185"/>
+      <c r="H27" s="185"/>
+      <c r="I27" s="185"/>
+      <c r="J27" s="185"/>
+      <c r="K27" s="185"/>
+      <c r="L27" s="186"/>
       <c r="M27" s="299"/>
       <c r="N27" s="299"/>
       <c r="O27" s="300"/>
@@ -11768,20 +11774,20 @@
       </c>
       <c r="F6" s="110"/>
       <c r="G6" s="111"/>
-      <c r="H6" s="112" t="s">
+      <c r="H6" s="107" t="s">
         <v>99</v>
       </c>
-      <c r="I6" s="113"/>
+      <c r="I6" s="112"/>
       <c r="J6" s="108"/>
-      <c r="K6" s="114" t="s">
+      <c r="K6" s="113" t="s">
         <v>100</v>
       </c>
-      <c r="L6" s="115"/>
-      <c r="M6" s="116">
+      <c r="L6" s="114"/>
+      <c r="M6" s="115">
         <v>46216</v>
       </c>
-      <c r="N6" s="117"/>
-      <c r="O6" s="118"/>
+      <c r="N6" s="116"/>
+      <c r="O6" s="117"/>
       <c r="P6" s="100"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:16">
@@ -11789,29 +11795,29 @@
         <v>101</v>
       </c>
       <c r="B7" s="106"/>
-      <c r="C7" s="112" t="s">
+      <c r="C7" s="107" t="s">
         <v>102</v>
       </c>
       <c r="D7" s="108"/>
-      <c r="E7" s="114" t="s">
+      <c r="E7" s="113" t="s">
         <v>103</v>
       </c>
-      <c r="F7" s="119"/>
-      <c r="G7" s="115"/>
-      <c r="H7" s="120" t="s">
+      <c r="F7" s="118"/>
+      <c r="G7" s="114"/>
+      <c r="H7" s="119" t="s">
         <v>104</v>
       </c>
-      <c r="I7" s="121"/>
-      <c r="J7" s="122"/>
-      <c r="K7" s="114" t="s">
+      <c r="I7" s="120"/>
+      <c r="J7" s="121"/>
+      <c r="K7" s="113" t="s">
         <v>105</v>
       </c>
-      <c r="L7" s="115"/>
-      <c r="M7" s="116">
-        <v>46311</v>
-      </c>
-      <c r="N7" s="117"/>
-      <c r="O7" s="118"/>
+      <c r="L7" s="114"/>
+      <c r="M7" s="115">
+        <v>46312</v>
+      </c>
+      <c r="N7" s="116"/>
+      <c r="O7" s="117"/>
       <c r="P7" s="100"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:16">
@@ -11819,19 +11825,19 @@
         <v>106</v>
       </c>
       <c r="B8" s="111"/>
-      <c r="C8" s="112" t="str">
+      <c r="C8" s="107" t="str">
         <f>'01. Tổng task'!H5</f>
         <v>2026-09</v>
       </c>
       <c r="D8" s="108"/>
-      <c r="E8" s="123" t="s">
+      <c r="E8" s="122" t="s">
         <v>107</v>
       </c>
-      <c r="F8" s="124"/>
-      <c r="G8" s="125"/>
-      <c r="H8" s="120"/>
-      <c r="I8" s="121"/>
-      <c r="J8" s="122"/>
+      <c r="F8" s="123"/>
+      <c r="G8" s="124"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="120"/>
+      <c r="J8" s="121"/>
       <c r="K8" s="100"/>
       <c r="L8" s="100"/>
       <c r="M8" s="100"/>
@@ -11840,20 +11846,20 @@
       <c r="P8" s="100"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:16">
-      <c r="A9" s="126"/>
-      <c r="B9" s="126"/>
-      <c r="C9" s="126"/>
-      <c r="D9" s="126"/>
-      <c r="E9" s="126"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="126"/>
-      <c r="H9" s="126"/>
-      <c r="I9" s="126"/>
-      <c r="J9" s="126"/>
-      <c r="K9" s="126"/>
-      <c r="L9" s="126"/>
-      <c r="M9" s="126"/>
-      <c r="N9" s="126"/>
+      <c r="A9" s="125"/>
+      <c r="B9" s="125"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="125"/>
+      <c r="F9" s="125"/>
+      <c r="G9" s="125"/>
+      <c r="H9" s="125"/>
+      <c r="I9" s="125"/>
+      <c r="J9" s="125"/>
+      <c r="K9" s="125"/>
+      <c r="L9" s="125"/>
+      <c r="M9" s="125"/>
+      <c r="N9" s="125"/>
       <c r="O9" s="100"/>
       <c r="P9" s="100"/>
     </row>
@@ -11910,134 +11916,134 @@
       <c r="P11" s="100"/>
     </row>
     <row r="12" ht="261.75" customHeight="1" spans="1:16">
-      <c r="A12" s="127">
+      <c r="A12" s="126">
         <v>1</v>
       </c>
-      <c r="B12" s="128" t="str" cm="1">
+      <c r="B12" s="127" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(INDEX('01. Tổng task'!$C$13:$C$109,MATCH(0,COUNTIF($B$11:B11,'01. Tổng task'!$C$13:$C$109)+IF('01. Tổng task'!$C$13:$C$109="",1,0),0)),"")</f>
         <v>[SW2026] ITS015 - Hữu Nghị-Chi Lăng</v>
       </c>
-      <c r="C12" s="129" t="str">
+      <c r="C12" s="128" t="str">
         <f>P12</f>
         <v>[2026] XD001.5.6 Service tích hợp dữ liệu 2
 XD001.6.3. Service tích hợp thiết bị</v>
       </c>
-      <c r="D12" s="130"/>
-      <c r="E12" s="130"/>
-      <c r="F12" s="130"/>
-      <c r="G12" s="129" t="s">
+      <c r="D12" s="129"/>
+      <c r="E12" s="129"/>
+      <c r="F12" s="129"/>
+      <c r="G12" s="128" t="s">
         <v>115</v>
       </c>
-      <c r="H12" s="130"/>
-      <c r="I12" s="130"/>
-      <c r="J12" s="130"/>
-      <c r="K12" s="130"/>
-      <c r="L12" s="130"/>
-      <c r="M12" s="131">
+      <c r="H12" s="129"/>
+      <c r="I12" s="129"/>
+      <c r="J12" s="129"/>
+      <c r="K12" s="129"/>
+      <c r="L12" s="129"/>
+      <c r="M12" s="130">
         <f>COUNTIF('01. Tổng task'!$C$13:$C$19,B12)</f>
         <v>2</v>
       </c>
-      <c r="N12" s="131">
+      <c r="N12" s="130">
         <f>SUMIF('01. Tổng task'!$C$13:$C$19,B12,'01. Tổng task'!$I$13:$I$19)</f>
         <v>8</v>
       </c>
-      <c r="O12" s="132">
+      <c r="O12" s="131">
         <f>IFERROR(SUMPRODUCT(('01. Tổng task'!$C$13:$C$19=$B12)*'01. Tổng task'!$I$13:$I$19*'01. Tổng task'!$AF$13:$AF$19)/SUMIF('01. Tổng task'!$C$13:$C$19,$B12,'01. Tổng task'!$I$13:$I$19),0)</f>
         <v>100</v>
       </c>
-      <c r="P12" s="130" t="str">
+      <c r="P12" s="129" t="str">
         <f t="array" ref="P12">IF($B12="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF('01. Tổng task'!$C$13:$C$109=$B12,'01. Tổng task'!$D$13:$D$109,"")))</f>
         <v>[2026] XD001.5.6 Service tích hợp dữ liệu 2
 XD001.6.3. Service tích hợp thiết bị</v>
       </c>
     </row>
     <row r="13" ht="95.1" customHeight="1" spans="1:16">
-      <c r="A13" s="127">
+      <c r="A13" s="126">
         <v>2</v>
       </c>
-      <c r="B13" s="128" t="str" cm="1">
+      <c r="B13" s="127" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(INDEX('01. Tổng task'!$C$13:$C$109,MATCH(0,COUNTIF($B$11:B12,'01. Tổng task'!$C$13:$C$109)+IF('01. Tổng task'!$C$13:$C$109="",1,0),0)),"")</f>
         <v/>
       </c>
-      <c r="C13" s="129" t="str">
+      <c r="C13" s="128" t="str">
         <f>P13</f>
         <v/>
       </c>
-      <c r="D13" s="130"/>
-      <c r="E13" s="130"/>
-      <c r="F13" s="130"/>
-      <c r="G13" s="129"/>
-      <c r="H13" s="130"/>
-      <c r="I13" s="130"/>
-      <c r="J13" s="130"/>
-      <c r="K13" s="130"/>
-      <c r="L13" s="130"/>
-      <c r="M13" s="131">
+      <c r="D13" s="129"/>
+      <c r="E13" s="129"/>
+      <c r="F13" s="129"/>
+      <c r="G13" s="128"/>
+      <c r="H13" s="129"/>
+      <c r="I13" s="129"/>
+      <c r="J13" s="129"/>
+      <c r="K13" s="129"/>
+      <c r="L13" s="129"/>
+      <c r="M13" s="130">
         <f>COUNTIF('01. Tổng task'!$C$13:$C$19,B13)</f>
         <v>0</v>
       </c>
-      <c r="N13" s="131">
+      <c r="N13" s="130">
         <f>SUMIF('01. Tổng task'!$C$13:$C$19,B13,'01. Tổng task'!$I$13:$I$19)</f>
         <v>0</v>
       </c>
-      <c r="O13" s="132" cm="1">
+      <c r="O13" s="131" cm="1">
         <f t="array" ref="O13">IFERROR(SUMPRODUCT(('01. Tổng task'!$C$13:$C$19=$B13)*'01. Tổng task'!$I$13:$I$19*'01. Tổng task'!$AF$13:$AF$19)/SUMIF('01. Tổng task'!$C$13:$C$19,$B13,'01. Tổng task'!$I$13:$I$19),0)</f>
         <v>0</v>
       </c>
-      <c r="P13" s="130" t="str">
+      <c r="P13" s="129" t="str">
         <f t="array" ref="P13">IF($B13="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF('01. Tổng task'!$C$13:$C$109=$B13,'01. Tổng task'!$D$13:$D$109,"")))</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:16">
-      <c r="A14" s="133" t="s">
+      <c r="A14" s="132" t="s">
         <v>116</v>
       </c>
-      <c r="B14" s="134"/>
-      <c r="C14" s="134"/>
-      <c r="D14" s="134"/>
-      <c r="E14" s="134"/>
-      <c r="F14" s="134"/>
-      <c r="G14" s="134"/>
-      <c r="H14" s="134"/>
-      <c r="I14" s="134"/>
-      <c r="J14" s="134"/>
-      <c r="K14" s="134"/>
-      <c r="L14" s="134"/>
-      <c r="M14" s="133">
+      <c r="B14" s="133"/>
+      <c r="C14" s="133"/>
+      <c r="D14" s="133"/>
+      <c r="E14" s="133"/>
+      <c r="F14" s="133"/>
+      <c r="G14" s="133"/>
+      <c r="H14" s="133"/>
+      <c r="I14" s="133"/>
+      <c r="J14" s="133"/>
+      <c r="K14" s="133"/>
+      <c r="L14" s="133"/>
+      <c r="M14" s="132">
         <f>SUM(M12:M13)</f>
         <v>1</v>
       </c>
-      <c r="N14" s="133">
+      <c r="N14" s="132">
         <f>SUM(N12:N13)</f>
         <v>0</v>
       </c>
-      <c r="O14" s="135">
+      <c r="O14" s="134">
         <f>IFERROR(AVERAGEIF(B12:B13,"?*",O12:O13),0)</f>
         <v>90.45</v>
       </c>
-      <c r="P14" s="134"/>
+      <c r="P14" s="133"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:16">
-      <c r="A15" s="136"/>
-      <c r="B15" s="136"/>
-      <c r="C15" s="136"/>
-      <c r="D15" s="136"/>
-      <c r="E15" s="136"/>
-      <c r="F15" s="136"/>
-      <c r="G15" s="136"/>
-      <c r="H15" s="136"/>
-      <c r="I15" s="136"/>
-      <c r="J15" s="136"/>
-      <c r="K15" s="136"/>
-      <c r="L15" s="136"/>
-      <c r="M15" s="136"/>
-      <c r="N15" s="136"/>
-      <c r="O15" s="137"/>
-      <c r="P15" s="137"/>
+      <c r="A15" s="135"/>
+      <c r="B15" s="135"/>
+      <c r="C15" s="135"/>
+      <c r="D15" s="135"/>
+      <c r="E15" s="135"/>
+      <c r="F15" s="135"/>
+      <c r="G15" s="135"/>
+      <c r="H15" s="135"/>
+      <c r="I15" s="135"/>
+      <c r="J15" s="135"/>
+      <c r="K15" s="135"/>
+      <c r="L15" s="135"/>
+      <c r="M15" s="135"/>
+      <c r="N15" s="135"/>
+      <c r="O15" s="136"/>
+      <c r="P15" s="136"/>
     </row>
     <row r="16" ht="40.5" customHeight="1" spans="1:16">
-      <c r="A16" s="138" t="s">
+      <c r="A16" s="137" t="s">
         <v>117</v>
       </c>
       <c r="B16" s="102"/>
@@ -12054,21 +12060,21 @@
       <c r="M16" s="102"/>
       <c r="N16" s="102"/>
       <c r="O16" s="103"/>
-      <c r="P16" s="130"/>
+      <c r="P16" s="129"/>
     </row>
     <row r="17" ht="43.5" customHeight="1" spans="1:16">
       <c r="A17" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="139" t="s">
+      <c r="B17" s="138" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="140"/>
-      <c r="D17" s="141" t="s">
+      <c r="C17" s="139"/>
+      <c r="D17" s="140" t="s">
         <v>119</v>
       </c>
-      <c r="E17" s="141"/>
-      <c r="F17" s="142"/>
+      <c r="E17" s="140"/>
+      <c r="F17" s="141"/>
       <c r="G17" s="54" t="s">
         <v>120</v>
       </c>
@@ -12090,190 +12096,190 @@
       <c r="M17" s="38"/>
       <c r="N17" s="38"/>
       <c r="O17" s="38"/>
-      <c r="P17" s="143"/>
+      <c r="P17" s="142"/>
     </row>
     <row r="18" ht="95.25" customHeight="1" spans="1:16">
-      <c r="A18" s="127">
+      <c r="A18" s="126">
         <v>1</v>
       </c>
-      <c r="B18" s="144" t="s">
+      <c r="B18" s="143" t="s">
         <v>126</v>
       </c>
-      <c r="C18" s="145"/>
-      <c r="D18" s="146" t="s">
+      <c r="C18" s="144"/>
+      <c r="D18" s="145" t="s">
         <v>127</v>
       </c>
-      <c r="E18" s="146"/>
-      <c r="F18" s="147"/>
-      <c r="G18" s="148">
+      <c r="E18" s="145"/>
+      <c r="F18" s="146"/>
+      <c r="G18" s="147">
         <v>0.4</v>
       </c>
-      <c r="H18" s="149">
+      <c r="H18" s="148">
         <v>8</v>
       </c>
-      <c r="I18" s="149"/>
-      <c r="J18" s="149">
+      <c r="I18" s="148"/>
+      <c r="J18" s="148">
         <f>H18*G18</f>
         <v>0</v>
       </c>
-      <c r="K18" s="149">
+      <c r="K18" s="148">
         <f>I18*G18</f>
         <v>0</v>
       </c>
-      <c r="L18" s="150"/>
-      <c r="M18" s="151"/>
-      <c r="N18" s="151"/>
-      <c r="O18" s="152"/>
-      <c r="P18" s="130"/>
+      <c r="L18" s="149"/>
+      <c r="M18" s="150"/>
+      <c r="N18" s="150"/>
+      <c r="O18" s="151"/>
+      <c r="P18" s="129"/>
     </row>
     <row r="19" ht="80.25" customHeight="1" spans="1:16">
-      <c r="A19" s="153">
+      <c r="A19" s="152">
         <v>2</v>
       </c>
-      <c r="B19" s="154" t="s">
+      <c r="B19" s="153" t="s">
         <v>128</v>
       </c>
-      <c r="C19" s="155"/>
-      <c r="D19" s="154" t="s">
+      <c r="C19" s="154"/>
+      <c r="D19" s="153" t="s">
         <v>129</v>
       </c>
-      <c r="E19" s="156"/>
-      <c r="F19" s="155"/>
-      <c r="G19" s="157">
+      <c r="E19" s="155"/>
+      <c r="F19" s="154"/>
+      <c r="G19" s="156">
         <v>0.3</v>
       </c>
-      <c r="H19" s="158">
+      <c r="H19" s="157">
         <v>8</v>
       </c>
-      <c r="I19" s="158"/>
-      <c r="J19" s="149">
+      <c r="I19" s="157"/>
+      <c r="J19" s="148">
         <f t="shared" ref="J19:J21" si="0">H19*G19</f>
         <v>0</v>
       </c>
-      <c r="K19" s="149">
+      <c r="K19" s="148">
         <f t="shared" ref="K19:K21" si="1">I19*G19</f>
         <v>0</v>
       </c>
-      <c r="L19" s="150"/>
-      <c r="M19" s="151"/>
-      <c r="N19" s="151"/>
-      <c r="O19" s="152"/>
-      <c r="P19" s="137"/>
+      <c r="L19" s="149"/>
+      <c r="M19" s="150"/>
+      <c r="N19" s="150"/>
+      <c r="O19" s="151"/>
+      <c r="P19" s="136"/>
     </row>
     <row r="20" ht="44.1" customHeight="1" spans="1:16">
-      <c r="A20" s="127">
+      <c r="A20" s="126">
         <v>3</v>
       </c>
-      <c r="B20" s="144" t="s">
+      <c r="B20" s="143" t="s">
         <v>130</v>
       </c>
-      <c r="C20" s="145"/>
-      <c r="D20" s="144" t="s">
+      <c r="C20" s="144"/>
+      <c r="D20" s="143" t="s">
         <v>131</v>
       </c>
-      <c r="E20" s="159"/>
-      <c r="F20" s="145"/>
-      <c r="G20" s="148">
+      <c r="E20" s="158"/>
+      <c r="F20" s="144"/>
+      <c r="G20" s="147">
         <v>0.2</v>
       </c>
-      <c r="H20" s="149">
+      <c r="H20" s="148">
         <v>8</v>
       </c>
-      <c r="I20" s="149"/>
-      <c r="J20" s="149">
+      <c r="I20" s="148"/>
+      <c r="J20" s="148">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K20" s="149">
+      <c r="K20" s="148">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L20" s="150"/>
-      <c r="M20" s="151"/>
-      <c r="N20" s="151"/>
-      <c r="O20" s="152"/>
-      <c r="P20" s="130"/>
+      <c r="L20" s="149"/>
+      <c r="M20" s="150"/>
+      <c r="N20" s="150"/>
+      <c r="O20" s="151"/>
+      <c r="P20" s="129"/>
     </row>
     <row r="21" ht="44.1" customHeight="1" spans="1:16">
-      <c r="A21" s="153">
+      <c r="A21" s="152">
         <v>4</v>
       </c>
-      <c r="B21" s="160" t="s">
+      <c r="B21" s="159" t="s">
         <v>132</v>
       </c>
-      <c r="C21" s="161"/>
-      <c r="D21" s="160" t="s">
+      <c r="C21" s="160"/>
+      <c r="D21" s="159" t="s">
         <v>133</v>
       </c>
-      <c r="E21" s="162"/>
-      <c r="F21" s="161"/>
-      <c r="G21" s="157">
+      <c r="E21" s="161"/>
+      <c r="F21" s="160"/>
+      <c r="G21" s="156">
         <v>0.1</v>
       </c>
-      <c r="H21" s="158">
+      <c r="H21" s="157">
         <v>8</v>
       </c>
-      <c r="I21" s="158"/>
-      <c r="J21" s="149">
+      <c r="I21" s="157"/>
+      <c r="J21" s="148">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K21" s="149">
+      <c r="K21" s="148">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L21" s="163"/>
-      <c r="M21" s="164"/>
-      <c r="N21" s="164"/>
-      <c r="O21" s="165"/>
-      <c r="P21" s="137"/>
+      <c r="L21" s="162"/>
+      <c r="M21" s="163"/>
+      <c r="N21" s="163"/>
+      <c r="O21" s="164"/>
+      <c r="P21" s="136"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:16">
-      <c r="A22" s="133" t="s">
+      <c r="A22" s="132" t="s">
         <v>116</v>
       </c>
-      <c r="B22" s="134"/>
-      <c r="C22" s="134"/>
-      <c r="D22" s="133"/>
-      <c r="E22" s="133"/>
-      <c r="F22" s="133"/>
-      <c r="G22" s="133">
+      <c r="B22" s="133"/>
+      <c r="C22" s="133"/>
+      <c r="D22" s="132"/>
+      <c r="E22" s="132"/>
+      <c r="F22" s="132"/>
+      <c r="G22" s="132">
         <f>SUM(G18:G21)</f>
         <v>1</v>
       </c>
-      <c r="H22" s="166"/>
-      <c r="I22" s="166"/>
-      <c r="J22" s="166">
+      <c r="H22" s="165"/>
+      <c r="I22" s="165"/>
+      <c r="J22" s="165">
         <f>SUM(J18:J21)</f>
         <v>0</v>
       </c>
-      <c r="K22" s="166">
+      <c r="K22" s="165">
         <f>SUM(K18:K21)</f>
         <v>0</v>
       </c>
-      <c r="L22" s="133"/>
-      <c r="M22" s="134"/>
-      <c r="N22" s="134"/>
-      <c r="O22" s="134"/>
-      <c r="P22" s="134"/>
+      <c r="L22" s="132"/>
+      <c r="M22" s="133"/>
+      <c r="N22" s="133"/>
+      <c r="O22" s="133"/>
+      <c r="P22" s="133"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:16">
-      <c r="A23" s="136"/>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
-      <c r="D23" s="136"/>
-      <c r="E23" s="136"/>
-      <c r="F23" s="136"/>
-      <c r="G23" s="136"/>
-      <c r="H23" s="136"/>
-      <c r="I23" s="136"/>
-      <c r="J23" s="136"/>
-      <c r="K23" s="136"/>
-      <c r="L23" s="136"/>
-      <c r="M23" s="136"/>
-      <c r="N23" s="136"/>
-      <c r="O23" s="137"/>
-      <c r="P23" s="137"/>
+      <c r="A23" s="135"/>
+      <c r="B23" s="135"/>
+      <c r="C23" s="135"/>
+      <c r="D23" s="135"/>
+      <c r="E23" s="135"/>
+      <c r="F23" s="135"/>
+      <c r="G23" s="135"/>
+      <c r="H23" s="135"/>
+      <c r="I23" s="135"/>
+      <c r="J23" s="135"/>
+      <c r="K23" s="135"/>
+      <c r="L23" s="135"/>
+      <c r="M23" s="135"/>
+      <c r="N23" s="135"/>
+      <c r="O23" s="136"/>
+      <c r="P23" s="136"/>
     </row>
     <row r="24" ht="24.9" customHeight="1" spans="1:16">
       <c r="A24" s="101" t="s">
@@ -12293,7 +12299,7 @@
       <c r="M24" s="102"/>
       <c r="N24" s="102"/>
       <c r="O24" s="103"/>
-      <c r="P24" s="130"/>
+      <c r="P24" s="129"/>
     </row>
     <row r="25" ht="30.75" customHeight="1" spans="1:16">
       <c r="A25" s="37" t="s">
@@ -12311,326 +12317,326 @@
         <v>15</v>
       </c>
       <c r="G25" s="39"/>
-      <c r="H25" s="136"/>
-      <c r="I25" s="136"/>
-      <c r="J25" s="136"/>
-      <c r="K25" s="136"/>
-      <c r="L25" s="136"/>
-      <c r="M25" s="136"/>
-      <c r="N25" s="136"/>
-      <c r="O25" s="137"/>
-      <c r="P25" s="137"/>
+      <c r="H25" s="135"/>
+      <c r="I25" s="135"/>
+      <c r="J25" s="135"/>
+      <c r="K25" s="135"/>
+      <c r="L25" s="135"/>
+      <c r="M25" s="135"/>
+      <c r="N25" s="135"/>
+      <c r="O25" s="136"/>
+      <c r="P25" s="136"/>
     </row>
     <row r="26" ht="24.9" customHeight="1" spans="1:16">
-      <c r="A26" s="129" t="s">
+      <c r="A26" s="128" t="s">
         <v>138</v>
       </c>
-      <c r="B26" s="130"/>
-      <c r="C26" s="148">
+      <c r="B26" s="129"/>
+      <c r="C26" s="147">
         <v>0.4</v>
       </c>
-      <c r="D26" s="167">
+      <c r="D26" s="166">
         <f>IFERROR(SUM('01. Tổng task'!$AH$13:$AH$516)/SUM('01. Tổng task'!$AL$13:$AL$516),0)</f>
         <v>98.3529411764706</v>
       </c>
-      <c r="E26" s="168"/>
-      <c r="F26" s="169">
+      <c r="E26" s="167"/>
+      <c r="F26" s="168">
         <f>C26*D26</f>
         <v>39.3411764705882</v>
       </c>
-      <c r="G26" s="130"/>
-      <c r="H26" s="128"/>
-      <c r="I26" s="128"/>
-      <c r="J26" s="128"/>
-      <c r="K26" s="128"/>
-      <c r="L26" s="128"/>
-      <c r="M26" s="128"/>
-      <c r="N26" s="128"/>
-      <c r="O26" s="130"/>
-      <c r="P26" s="130"/>
+      <c r="G26" s="129"/>
+      <c r="H26" s="127"/>
+      <c r="I26" s="127"/>
+      <c r="J26" s="127"/>
+      <c r="K26" s="127"/>
+      <c r="L26" s="127"/>
+      <c r="M26" s="127"/>
+      <c r="N26" s="127"/>
+      <c r="O26" s="129"/>
+      <c r="P26" s="129"/>
     </row>
     <row r="27" ht="24.9" customHeight="1" spans="1:16">
-      <c r="A27" s="170" t="s">
+      <c r="A27" s="169" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="137"/>
-      <c r="C27" s="157">
+      <c r="B27" s="136"/>
+      <c r="C27" s="156">
         <v>0.35</v>
       </c>
-      <c r="D27" s="171">
+      <c r="D27" s="170">
         <f>IFERROR(SUM('01. Tổng task'!$AI$13:$AI$516)/SUM('01. Tổng task'!$AM$13:$AM$516),0)</f>
         <v>94.8333333333333</v>
       </c>
-      <c r="E27" s="172"/>
-      <c r="F27" s="173">
+      <c r="E27" s="171"/>
+      <c r="F27" s="172">
         <f>C27*D27</f>
         <v>33.1916666666667</v>
       </c>
-      <c r="G27" s="137"/>
-      <c r="H27" s="136"/>
-      <c r="I27" s="136"/>
-      <c r="J27" s="136"/>
-      <c r="K27" s="136"/>
-      <c r="L27" s="136"/>
-      <c r="M27" s="136"/>
-      <c r="N27" s="136"/>
-      <c r="O27" s="137"/>
-      <c r="P27" s="137"/>
+      <c r="G27" s="136"/>
+      <c r="H27" s="135"/>
+      <c r="I27" s="135"/>
+      <c r="J27" s="135"/>
+      <c r="K27" s="135"/>
+      <c r="L27" s="135"/>
+      <c r="M27" s="135"/>
+      <c r="N27" s="135"/>
+      <c r="O27" s="136"/>
+      <c r="P27" s="136"/>
     </row>
     <row r="28" ht="24.9" customHeight="1" spans="1:16">
-      <c r="A28" s="129" t="s">
+      <c r="A28" s="128" t="s">
         <v>140</v>
       </c>
-      <c r="B28" s="130"/>
-      <c r="C28" s="148">
+      <c r="B28" s="129"/>
+      <c r="C28" s="147">
         <v>0.15</v>
       </c>
-      <c r="D28" s="167">
+      <c r="D28" s="166">
         <f>IFERROR(SUM('01. Tổng task'!$AJ$13:$AJ$516)/SUM('01. Tổng task'!$AN$13:$AN$516),0)</f>
         <v>100</v>
       </c>
-      <c r="E28" s="168"/>
-      <c r="F28" s="169">
+      <c r="E28" s="167"/>
+      <c r="F28" s="168">
         <f>C28*D28</f>
         <v>15</v>
       </c>
-      <c r="G28" s="130"/>
-      <c r="H28" s="128"/>
-      <c r="I28" s="128"/>
-      <c r="J28" s="128"/>
-      <c r="K28" s="128"/>
-      <c r="L28" s="128"/>
-      <c r="M28" s="128"/>
-      <c r="N28" s="128"/>
-      <c r="O28" s="130"/>
-      <c r="P28" s="130"/>
+      <c r="G28" s="129"/>
+      <c r="H28" s="127"/>
+      <c r="I28" s="127"/>
+      <c r="J28" s="127"/>
+      <c r="K28" s="127"/>
+      <c r="L28" s="127"/>
+      <c r="M28" s="127"/>
+      <c r="N28" s="127"/>
+      <c r="O28" s="129"/>
+      <c r="P28" s="129"/>
     </row>
     <row r="29" ht="24.9" customHeight="1" spans="1:16">
-      <c r="A29" s="170" t="s">
+      <c r="A29" s="169" t="s">
         <v>141</v>
       </c>
-      <c r="B29" s="137"/>
-      <c r="C29" s="157">
+      <c r="B29" s="136"/>
+      <c r="C29" s="156">
         <v>0.1</v>
       </c>
-      <c r="D29" s="171">
+      <c r="D29" s="170">
         <f>IFERROR(SUM('01. Tổng task'!$AK$13:$AK$19)/SUM('01. Tổng task'!$AO$13:$AO$19),0)</f>
         <v>87.6875</v>
       </c>
-      <c r="E29" s="172"/>
-      <c r="F29" s="173">
+      <c r="E29" s="171"/>
+      <c r="F29" s="172">
         <f>C29*D29</f>
         <v>8.76875</v>
       </c>
-      <c r="G29" s="137"/>
-      <c r="H29" s="136"/>
-      <c r="I29" s="136"/>
-      <c r="J29" s="136"/>
-      <c r="K29" s="136"/>
-      <c r="L29" s="136"/>
-      <c r="M29" s="136"/>
-      <c r="N29" s="136"/>
-      <c r="O29" s="137"/>
-      <c r="P29" s="137"/>
+      <c r="G29" s="136"/>
+      <c r="H29" s="135"/>
+      <c r="I29" s="135"/>
+      <c r="J29" s="135"/>
+      <c r="K29" s="135"/>
+      <c r="L29" s="135"/>
+      <c r="M29" s="135"/>
+      <c r="N29" s="135"/>
+      <c r="O29" s="136"/>
+      <c r="P29" s="136"/>
     </row>
     <row r="30" ht="24.9" customHeight="1" spans="1:16">
-      <c r="A30" s="174" t="s">
+      <c r="A30" s="173" t="s">
         <v>142</v>
       </c>
-      <c r="B30" s="175"/>
-      <c r="C30" s="176">
+      <c r="B30" s="174"/>
+      <c r="C30" s="175">
         <v>1</v>
       </c>
-      <c r="D30" s="177"/>
-      <c r="E30" s="175"/>
-      <c r="F30" s="177">
+      <c r="D30" s="176"/>
+      <c r="E30" s="174"/>
+      <c r="F30" s="176">
         <f>SUM($F$26:$F$29)</f>
         <v>96.3015931372549</v>
       </c>
-      <c r="G30" s="175"/>
-      <c r="H30" s="128"/>
-      <c r="I30" s="128"/>
-      <c r="J30" s="128"/>
-      <c r="K30" s="128"/>
-      <c r="L30" s="128"/>
-      <c r="M30" s="128"/>
-      <c r="N30" s="128"/>
-      <c r="O30" s="128"/>
-      <c r="P30" s="134"/>
+      <c r="G30" s="174"/>
+      <c r="H30" s="127"/>
+      <c r="I30" s="127"/>
+      <c r="J30" s="127"/>
+      <c r="K30" s="127"/>
+      <c r="L30" s="127"/>
+      <c r="M30" s="127"/>
+      <c r="N30" s="127"/>
+      <c r="O30" s="127"/>
+      <c r="P30" s="133"/>
     </row>
     <row r="31" s="91" customFormat="1" ht="24.9" customHeight="1" spans="1:16">
-      <c r="A31" s="178"/>
-      <c r="B31" s="179"/>
-      <c r="C31" s="180"/>
-      <c r="D31" s="181"/>
-      <c r="E31" s="179"/>
-      <c r="F31" s="181"/>
-      <c r="G31" s="179"/>
-      <c r="H31" s="145"/>
-      <c r="I31" s="128"/>
-      <c r="J31" s="128"/>
-      <c r="K31" s="128"/>
-      <c r="L31" s="128"/>
-      <c r="M31" s="128"/>
-      <c r="N31" s="128"/>
-      <c r="O31" s="128"/>
-      <c r="P31" s="182"/>
+      <c r="A31" s="177"/>
+      <c r="B31" s="178"/>
+      <c r="C31" s="179"/>
+      <c r="D31" s="180"/>
+      <c r="E31" s="178"/>
+      <c r="F31" s="180"/>
+      <c r="G31" s="178"/>
+      <c r="H31" s="144"/>
+      <c r="I31" s="127"/>
+      <c r="J31" s="127"/>
+      <c r="K31" s="127"/>
+      <c r="L31" s="127"/>
+      <c r="M31" s="127"/>
+      <c r="N31" s="127"/>
+      <c r="O31" s="127"/>
+      <c r="P31" s="181"/>
     </row>
     <row r="32" s="91" customFormat="1" ht="24.9" customHeight="1" spans="1:16">
-      <c r="A32" s="178"/>
-      <c r="B32" s="179"/>
-      <c r="C32" s="180"/>
-      <c r="D32" s="181"/>
-      <c r="E32" s="179"/>
-      <c r="F32" s="181"/>
-      <c r="G32" s="179"/>
-      <c r="H32" s="145"/>
-      <c r="I32" s="128"/>
-      <c r="J32" s="128"/>
-      <c r="K32" s="128"/>
-      <c r="L32" s="128"/>
-      <c r="M32" s="128"/>
-      <c r="N32" s="128"/>
-      <c r="O32" s="128"/>
-      <c r="P32" s="182"/>
+      <c r="A32" s="177"/>
+      <c r="B32" s="178"/>
+      <c r="C32" s="179"/>
+      <c r="D32" s="180"/>
+      <c r="E32" s="178"/>
+      <c r="F32" s="180"/>
+      <c r="G32" s="178"/>
+      <c r="H32" s="144"/>
+      <c r="I32" s="127"/>
+      <c r="J32" s="127"/>
+      <c r="K32" s="127"/>
+      <c r="L32" s="127"/>
+      <c r="M32" s="127"/>
+      <c r="N32" s="127"/>
+      <c r="O32" s="127"/>
+      <c r="P32" s="181"/>
     </row>
     <row r="33" s="91" customFormat="1" ht="24.9" customHeight="1" spans="1:16">
-      <c r="A33" s="178"/>
-      <c r="B33" s="179"/>
-      <c r="C33" s="180"/>
-      <c r="D33" s="181"/>
-      <c r="E33" s="179"/>
-      <c r="F33" s="181"/>
-      <c r="G33" s="179"/>
-      <c r="H33" s="145"/>
-      <c r="I33" s="128"/>
-      <c r="J33" s="128"/>
-      <c r="K33" s="128"/>
-      <c r="L33" s="128"/>
-      <c r="M33" s="128"/>
-      <c r="N33" s="128"/>
-      <c r="O33" s="128"/>
-      <c r="P33" s="182"/>
+      <c r="A33" s="177"/>
+      <c r="B33" s="178"/>
+      <c r="C33" s="179"/>
+      <c r="D33" s="180"/>
+      <c r="E33" s="178"/>
+      <c r="F33" s="180"/>
+      <c r="G33" s="178"/>
+      <c r="H33" s="144"/>
+      <c r="I33" s="127"/>
+      <c r="J33" s="127"/>
+      <c r="K33" s="127"/>
+      <c r="L33" s="127"/>
+      <c r="M33" s="127"/>
+      <c r="N33" s="127"/>
+      <c r="O33" s="127"/>
+      <c r="P33" s="181"/>
     </row>
     <row r="34" ht="20.1" customHeight="1" spans="1:16">
-      <c r="A34" s="183"/>
-      <c r="B34" s="183"/>
-      <c r="C34" s="183"/>
-      <c r="D34" s="183"/>
-      <c r="E34" s="183"/>
-      <c r="F34" s="183"/>
-      <c r="G34" s="183"/>
-      <c r="H34" s="136"/>
-      <c r="I34" s="184"/>
-      <c r="J34" s="184"/>
-      <c r="K34" s="184"/>
-      <c r="L34" s="184"/>
-      <c r="M34" s="136"/>
-      <c r="N34" s="136"/>
-      <c r="O34" s="137"/>
-      <c r="P34" s="137"/>
+      <c r="A34" s="182"/>
+      <c r="B34" s="182"/>
+      <c r="C34" s="182"/>
+      <c r="D34" s="182"/>
+      <c r="E34" s="182"/>
+      <c r="F34" s="182"/>
+      <c r="G34" s="182"/>
+      <c r="H34" s="135"/>
+      <c r="I34" s="183"/>
+      <c r="J34" s="183"/>
+      <c r="K34" s="183"/>
+      <c r="L34" s="183"/>
+      <c r="M34" s="135"/>
+      <c r="N34" s="135"/>
+      <c r="O34" s="136"/>
+      <c r="P34" s="136"/>
     </row>
     <row r="35" s="91" customFormat="1" ht="29.25" customHeight="1" spans="1:16">
-      <c r="A35" s="185" t="s">
+      <c r="A35" s="184" t="s">
         <v>143</v>
       </c>
-      <c r="B35" s="186"/>
-      <c r="C35" s="186"/>
-      <c r="D35" s="186"/>
-      <c r="E35" s="186"/>
-      <c r="F35" s="186"/>
-      <c r="G35" s="187"/>
-      <c r="H35" s="155"/>
-      <c r="I35" s="185" t="s">
+      <c r="B35" s="185"/>
+      <c r="C35" s="185"/>
+      <c r="D35" s="185"/>
+      <c r="E35" s="185"/>
+      <c r="F35" s="185"/>
+      <c r="G35" s="186"/>
+      <c r="H35" s="154"/>
+      <c r="I35" s="184" t="s">
         <v>75</v>
       </c>
-      <c r="J35" s="186"/>
-      <c r="K35" s="186"/>
-      <c r="L35" s="187"/>
-      <c r="M35" s="155"/>
-      <c r="N35" s="136"/>
-      <c r="O35" s="137"/>
-      <c r="P35" s="137"/>
+      <c r="J35" s="185"/>
+      <c r="K35" s="185"/>
+      <c r="L35" s="186"/>
+      <c r="M35" s="154"/>
+      <c r="N35" s="135"/>
+      <c r="O35" s="136"/>
+      <c r="P35" s="136"/>
     </row>
     <row r="36" ht="30" customHeight="1" spans="1:16">
-      <c r="A36" s="188" t="s">
+      <c r="A36" s="187" t="s">
         <v>144</v>
       </c>
-      <c r="B36" s="189"/>
+      <c r="B36" s="188"/>
       <c r="C36" s="54" t="s">
         <v>145</v>
       </c>
-      <c r="D36" s="188" t="s">
+      <c r="D36" s="187" t="s">
         <v>23</v>
       </c>
-      <c r="E36" s="190"/>
-      <c r="F36" s="190"/>
-      <c r="G36" s="189"/>
-      <c r="H36" s="145"/>
+      <c r="E36" s="189"/>
+      <c r="F36" s="189"/>
+      <c r="G36" s="188"/>
+      <c r="H36" s="144"/>
       <c r="I36" s="27"/>
       <c r="J36" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="K36" s="191" t="s">
+      <c r="K36" s="190" t="s">
         <v>78</v>
       </c>
-      <c r="L36" s="192" t="str">
+      <c r="L36" s="191" t="str">
         <f>_xlfn.UNICHAR(9733)&amp;_xlfn.UNICHAR(9733)&amp;_xlfn.UNICHAR(9733)&amp;_xlfn.UNICHAR(9733)&amp;_xlfn.UNICHAR(9733)</f>
         <v>★★★★★</v>
       </c>
-      <c r="M36" s="145"/>
-      <c r="N36" s="128"/>
-      <c r="O36" s="130"/>
-      <c r="P36" s="130"/>
+      <c r="M36" s="144"/>
+      <c r="N36" s="127"/>
+      <c r="O36" s="129"/>
+      <c r="P36" s="129"/>
     </row>
     <row r="37" ht="33.9" customHeight="1" spans="1:16">
-      <c r="A37" s="193" t="s">
+      <c r="A37" s="192" t="s">
         <v>146</v>
       </c>
-      <c r="B37" s="194"/>
-      <c r="C37" s="131">
+      <c r="B37" s="193"/>
+      <c r="C37" s="130">
         <f>COUNT('01. Tổng task'!$A$13:$A$516)</f>
         <v>2</v>
       </c>
-      <c r="D37" s="195" t="s">
+      <c r="D37" s="194" t="s">
         <v>147</v>
       </c>
-      <c r="E37" s="196"/>
-      <c r="F37" s="196"/>
-      <c r="G37" s="197"/>
-      <c r="H37" s="155"/>
+      <c r="E37" s="195"/>
+      <c r="F37" s="195"/>
+      <c r="G37" s="196"/>
+      <c r="H37" s="154"/>
       <c r="I37" s="30"/>
       <c r="J37" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="K37" s="198" t="s">
+      <c r="K37" s="197" t="s">
         <v>82</v>
       </c>
-      <c r="L37" s="199" t="str">
+      <c r="L37" s="198" t="str">
         <f>_xlfn.UNICHAR(9733)&amp;_xlfn.UNICHAR(9733)&amp;_xlfn.UNICHAR(9733)&amp;_xlfn.UNICHAR(9733)</f>
         <v>★★★★</v>
       </c>
-      <c r="M37" s="155"/>
-      <c r="N37" s="136"/>
-      <c r="O37" s="137"/>
-      <c r="P37" s="137"/>
+      <c r="M37" s="154"/>
+      <c r="N37" s="135"/>
+      <c r="O37" s="136"/>
+      <c r="P37" s="136"/>
     </row>
     <row r="38" ht="33.9" customHeight="1" spans="1:16">
-      <c r="A38" s="200" t="s">
+      <c r="A38" s="199" t="s">
         <v>148</v>
       </c>
-      <c r="B38" s="201"/>
-      <c r="C38" s="202">
+      <c r="B38" s="200"/>
+      <c r="C38" s="201">
         <f>SUMIFS('01. Tổng task'!$I$13:$I$516,'01. Tổng task'!$A$13:$A$516,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="D38" s="203" t="s">
+      <c r="D38" s="202" t="s">
         <v>149</v>
       </c>
-      <c r="E38" s="204"/>
-      <c r="F38" s="204"/>
-      <c r="G38" s="205"/>
-      <c r="H38" s="145"/>
+      <c r="E38" s="203"/>
+      <c r="F38" s="203"/>
+      <c r="G38" s="204"/>
+      <c r="H38" s="144"/>
       <c r="I38" s="30"/>
       <c r="J38" s="31" t="s">
         <v>85</v>
@@ -12638,31 +12644,31 @@
       <c r="K38" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="L38" s="107" t="str">
+      <c r="L38" s="205" t="str">
         <f>_xlfn.UNICHAR(9733)&amp;_xlfn.UNICHAR(9733)&amp;_xlfn.UNICHAR(9733)</f>
         <v>★★★</v>
       </c>
-      <c r="M38" s="145"/>
-      <c r="N38" s="128"/>
-      <c r="O38" s="130"/>
-      <c r="P38" s="130"/>
+      <c r="M38" s="144"/>
+      <c r="N38" s="127"/>
+      <c r="O38" s="129"/>
+      <c r="P38" s="129"/>
     </row>
     <row r="39" ht="33.9" customHeight="1" spans="1:16">
-      <c r="A39" s="193" t="s">
+      <c r="A39" s="192" t="s">
         <v>150</v>
       </c>
-      <c r="B39" s="194"/>
+      <c r="B39" s="193"/>
       <c r="C39" s="206">
         <f>IFERROR(SUMIFS('01. Tổng task'!$AG$13:$AG$516,'01. Tổng task'!$A$13:$A$516,"&gt;0")/SUMIFS('01. Tổng task'!$I$13:$I$516,'01. Tổng task'!$A$13:$A$516,"&gt;0"),0)</f>
         <v>0</v>
       </c>
-      <c r="D39" s="195" t="s">
+      <c r="D39" s="194" t="s">
         <v>151</v>
       </c>
-      <c r="E39" s="196"/>
-      <c r="F39" s="196"/>
-      <c r="G39" s="197"/>
-      <c r="H39" s="155"/>
+      <c r="E39" s="195"/>
+      <c r="F39" s="195"/>
+      <c r="G39" s="196"/>
+      <c r="H39" s="154"/>
       <c r="I39" s="30"/>
       <c r="J39" s="31" t="s">
         <v>89</v>
@@ -12674,27 +12680,27 @@
         <f>_xlfn.UNICHAR(9733)&amp;_xlfn.UNICHAR(9733)</f>
         <v>★★</v>
       </c>
-      <c r="M39" s="155"/>
-      <c r="N39" s="136"/>
-      <c r="O39" s="137"/>
-      <c r="P39" s="137"/>
+      <c r="M39" s="154"/>
+      <c r="N39" s="135"/>
+      <c r="O39" s="136"/>
+      <c r="P39" s="136"/>
     </row>
     <row r="40" ht="33.9" customHeight="1" spans="1:16">
-      <c r="A40" s="200" t="s">
+      <c r="A40" s="199" t="s">
         <v>152</v>
       </c>
-      <c r="B40" s="201"/>
+      <c r="B40" s="200"/>
       <c r="C40" s="208">
         <f>SUM($F$26:$F$29)</f>
         <v>96.3015931372549</v>
       </c>
-      <c r="D40" s="203" t="s">
+      <c r="D40" s="202" t="s">
         <v>153</v>
       </c>
-      <c r="E40" s="204"/>
-      <c r="F40" s="204"/>
-      <c r="G40" s="205"/>
-      <c r="H40" s="145"/>
+      <c r="E40" s="203"/>
+      <c r="F40" s="203"/>
+      <c r="G40" s="204"/>
+      <c r="H40" s="144"/>
       <c r="I40" s="34"/>
       <c r="J40" s="35" t="s">
         <v>93</v>
@@ -12706,41 +12712,41 @@
         <f>_xlfn.UNICHAR(9888)</f>
         <v>⚠</v>
       </c>
-      <c r="M40" s="145"/>
-      <c r="N40" s="128"/>
-      <c r="O40" s="130"/>
-      <c r="P40" s="130"/>
+      <c r="M40" s="144"/>
+      <c r="N40" s="127"/>
+      <c r="O40" s="129"/>
+      <c r="P40" s="129"/>
     </row>
     <row r="41" ht="43.5" customHeight="1" spans="1:16">
-      <c r="A41" s="193" t="s">
+      <c r="A41" s="192" t="s">
         <v>154</v>
       </c>
-      <c r="B41" s="194"/>
+      <c r="B41" s="193"/>
       <c r="C41" s="206">
         <f>IFERROR($K$22/10*80+$J$22/10*20,0)</f>
         <v>0</v>
       </c>
-      <c r="D41" s="195" t="s">
+      <c r="D41" s="194" t="s">
         <v>155</v>
       </c>
-      <c r="E41" s="196"/>
-      <c r="F41" s="196"/>
-      <c r="G41" s="197"/>
-      <c r="H41" s="155"/>
-      <c r="I41" s="136"/>
-      <c r="J41" s="136"/>
-      <c r="K41" s="136"/>
+      <c r="E41" s="195"/>
+      <c r="F41" s="195"/>
+      <c r="G41" s="196"/>
+      <c r="H41" s="154"/>
+      <c r="I41" s="135"/>
+      <c r="J41" s="135"/>
+      <c r="K41" s="135"/>
       <c r="L41" s="210"/>
-      <c r="M41" s="136"/>
-      <c r="N41" s="136"/>
-      <c r="O41" s="137"/>
-      <c r="P41" s="137"/>
+      <c r="M41" s="135"/>
+      <c r="N41" s="135"/>
+      <c r="O41" s="136"/>
+      <c r="P41" s="136"/>
     </row>
     <row r="42" ht="33.9" customHeight="1" spans="1:16">
-      <c r="A42" s="200" t="s">
+      <c r="A42" s="199" t="s">
         <v>156</v>
       </c>
-      <c r="B42" s="201"/>
+      <c r="B42" s="200"/>
       <c r="C42" s="208">
         <f>C40*80%+C41*20%</f>
         <v>77.0412745098039</v>
@@ -12751,15 +12757,15 @@
       <c r="E42" s="212"/>
       <c r="F42" s="212"/>
       <c r="G42" s="213"/>
-      <c r="H42" s="145"/>
-      <c r="I42" s="128"/>
-      <c r="J42" s="128"/>
-      <c r="K42" s="128"/>
-      <c r="L42" s="128"/>
-      <c r="M42" s="128"/>
-      <c r="N42" s="128"/>
-      <c r="O42" s="130"/>
-      <c r="P42" s="130"/>
+      <c r="H42" s="144"/>
+      <c r="I42" s="127"/>
+      <c r="J42" s="127"/>
+      <c r="K42" s="127"/>
+      <c r="L42" s="127"/>
+      <c r="M42" s="127"/>
+      <c r="N42" s="127"/>
+      <c r="O42" s="129"/>
+      <c r="P42" s="129"/>
     </row>
     <row r="43" ht="42.75" customHeight="1" spans="1:16">
       <c r="A43" s="214" t="s">
@@ -12777,33 +12783,33 @@
       <c r="E43" s="217"/>
       <c r="F43" s="217"/>
       <c r="G43" s="215"/>
-      <c r="H43" s="136"/>
-      <c r="I43" s="136"/>
-      <c r="J43" s="136"/>
-      <c r="K43" s="136"/>
-      <c r="L43" s="136"/>
-      <c r="M43" s="136"/>
-      <c r="N43" s="136"/>
-      <c r="O43" s="137"/>
-      <c r="P43" s="137"/>
+      <c r="H43" s="135"/>
+      <c r="I43" s="135"/>
+      <c r="J43" s="135"/>
+      <c r="K43" s="135"/>
+      <c r="L43" s="135"/>
+      <c r="M43" s="135"/>
+      <c r="N43" s="135"/>
+      <c r="O43" s="136"/>
+      <c r="P43" s="136"/>
     </row>
     <row r="44" s="91" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
-      <c r="A44" s="153"/>
-      <c r="B44" s="137"/>
+      <c r="A44" s="152"/>
+      <c r="B44" s="136"/>
       <c r="C44" s="218"/>
-      <c r="D44" s="153"/>
-      <c r="E44" s="137"/>
-      <c r="F44" s="137"/>
-      <c r="G44" s="137"/>
-      <c r="H44" s="136"/>
-      <c r="I44" s="136"/>
-      <c r="J44" s="136"/>
-      <c r="K44" s="136"/>
-      <c r="L44" s="136"/>
-      <c r="M44" s="136"/>
-      <c r="N44" s="136"/>
-      <c r="O44" s="137"/>
-      <c r="P44" s="137"/>
+      <c r="D44" s="152"/>
+      <c r="E44" s="136"/>
+      <c r="F44" s="136"/>
+      <c r="G44" s="136"/>
+      <c r="H44" s="135"/>
+      <c r="I44" s="135"/>
+      <c r="J44" s="135"/>
+      <c r="K44" s="135"/>
+      <c r="L44" s="135"/>
+      <c r="M44" s="135"/>
+      <c r="N44" s="135"/>
+      <c r="O44" s="136"/>
+      <c r="P44" s="136"/>
     </row>
     <row r="45" ht="24.9" customHeight="1" spans="1:16">
       <c r="A45" s="101" t="s">
@@ -13143,11 +13149,13 @@
       <c r="O59" s="39"/>
       <c r="P59" s="100"/>
     </row>
-    <row r="60" ht="54.75" customHeight="1" spans="1:16">
+    <row r="60" ht="65" customHeight="1" spans="1:16">
       <c r="A60" s="223" t="s">
         <v>182</v>
       </c>
-      <c r="B60" s="224"/>
+      <c r="B60" s="224" t="s">
+        <v>183</v>
+      </c>
       <c r="C60" s="100"/>
       <c r="D60" s="100"/>
       <c r="E60" s="100"/>
@@ -13163,11 +13171,13 @@
       <c r="O60" s="100"/>
       <c r="P60" s="100"/>
     </row>
-    <row r="61" ht="31.5" customHeight="1" spans="1:16">
+    <row r="61" ht="105" customHeight="1" spans="1:16">
       <c r="A61" s="223" t="s">
-        <v>183</v>
-      </c>
-      <c r="B61" s="219"/>
+        <v>184</v>
+      </c>
+      <c r="B61" s="224" t="s">
+        <v>185</v>
+      </c>
       <c r="C61" s="100"/>
       <c r="D61" s="100"/>
       <c r="E61" s="100"/>
@@ -13185,7 +13195,7 @@
     </row>
     <row r="62" ht="20.1" customHeight="1" spans="1:16">
       <c r="A62" s="223" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B62" s="225"/>
       <c r="C62" s="225"/>
@@ -13194,7 +13204,7 @@
       <c r="F62" s="225"/>
       <c r="G62" s="225"/>
       <c r="H62" s="223" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I62" s="225"/>
       <c r="J62" s="225"/>
@@ -13443,7 +13453,7 @@
   <sheetData>
     <row r="1" s="47" customFormat="1" ht="30.75" customHeight="1" spans="1:10">
       <c r="A1" s="51" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B1" s="52"/>
       <c r="C1" s="52"/>
@@ -13456,19 +13466,19 @@
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:10">
       <c r="A3" s="54" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B3" s="54" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D3" s="54" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E3" s="54" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" ht="30.75" customHeight="1" spans="1:10">
@@ -13482,10 +13492,10 @@
         <v>70</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" ht="28.5" customHeight="1" spans="1:10">
@@ -13497,10 +13507,10 @@
         <v>30</v>
       </c>
       <c r="D5" s="60" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E5" s="58" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" ht="57" customHeight="1" spans="1:10">
@@ -13514,40 +13524,40 @@
         <v>40</v>
       </c>
       <c r="D6" s="63" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" ht="42.75" customHeight="1" spans="1:10">
       <c r="A7" s="64"/>
       <c r="B7" s="62" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C7" s="62">
         <v>40</v>
       </c>
       <c r="D7" s="63" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E7" s="58" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" ht="71.25" customHeight="1" spans="1:10">
       <c r="A8" s="64"/>
       <c r="B8" s="62" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C8" s="62">
         <v>20</v>
       </c>
       <c r="D8" s="60" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H8" s="65"/>
       <c r="I8" s="65"/>
@@ -13564,10 +13574,10 @@
         <v>60</v>
       </c>
       <c r="D9" s="68" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E9" s="58" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10" ht="42.75" customHeight="1" spans="1:10">
@@ -13579,10 +13589,10 @@
         <v>20</v>
       </c>
       <c r="D10" s="60" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E10" s="70" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" ht="42.75" customHeight="1" spans="1:10">
@@ -13594,10 +13604,10 @@
         <v>20</v>
       </c>
       <c r="D11" s="60" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E11" s="58" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" ht="71.25" customHeight="1" spans="1:10">
@@ -13611,10 +13621,10 @@
         <v>25</v>
       </c>
       <c r="D12" s="63" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F12" s="73"/>
     </row>
@@ -13627,10 +13637,10 @@
         <v>25</v>
       </c>
       <c r="D13" s="63" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E13" s="58" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" ht="99.6" customHeight="1" spans="1:10">
@@ -13642,10 +13652,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="60" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E14" s="77" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" ht="128.25" customHeight="1" spans="1:10">
@@ -13657,10 +13667,10 @@
         <v>20</v>
       </c>
       <c r="D15" s="60" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E15" s="58" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16" ht="128.25" customHeight="1" spans="1:10">
@@ -13672,15 +13682,15 @@
         <v>20</v>
       </c>
       <c r="D16" s="60" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E16" s="58" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" s="47" customFormat="1" ht="30" customHeight="1" spans="1:6">
       <c r="A18" s="51" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B18" s="52"/>
       <c r="C18" s="52"/>
@@ -13696,43 +13706,43 @@
     </row>
     <row r="20" s="47" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="A20" s="79" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B20" s="79" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C20" s="79" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D20" s="79" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E20" s="79" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" s="47" customFormat="1" ht="30" customHeight="1" spans="1:6">
       <c r="A21" s="80" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B21" s="81" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C21" s="82">
         <v>1</v>
       </c>
       <c r="D21" s="80"/>
       <c r="E21" s="83" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F21" s="84"/>
     </row>
     <row r="22" s="47" customFormat="1" ht="30" customHeight="1" spans="1:6">
       <c r="A22" s="80" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B22" s="81" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C22" s="82">
         <v>2</v>
@@ -13743,10 +13753,10 @@
     </row>
     <row r="23" s="47" customFormat="1" ht="30" customHeight="1" spans="1:6">
       <c r="A23" s="80" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B23" s="81" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C23" s="82">
         <v>3</v>
@@ -13757,10 +13767,10 @@
     </row>
     <row r="24" s="47" customFormat="1" ht="30" customHeight="1" spans="1:6">
       <c r="A24" s="80" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B24" s="81" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C24" s="82">
         <v>4</v>
@@ -13771,10 +13781,10 @@
     </row>
     <row r="25" s="47" customFormat="1" ht="30" customHeight="1" spans="1:6">
       <c r="A25" s="80" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B25" s="81" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C25" s="82">
         <v>5</v>
@@ -13789,7 +13799,7 @@
     </row>
     <row r="27" ht="32.25" customHeight="1" spans="1:6">
       <c r="A27" s="86" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B27" s="87"/>
       <c r="C27" s="87"/>
@@ -13805,212 +13815,212 @@
     </row>
     <row r="29" s="48" customFormat="1" ht="17.25" customHeight="1" spans="1:6">
       <c r="A29" s="54" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B29" s="54" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C29" s="54"/>
       <c r="D29" s="54" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E29" s="54" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="30" s="48" customFormat="1" ht="28.5" customHeight="1" spans="1:6">
       <c r="A30" s="88" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B30" s="60" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C30" s="89"/>
       <c r="D30" s="90" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E30" s="90" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31" s="48" customFormat="1" ht="28.5" customHeight="1" spans="1:6">
       <c r="A31" s="88" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B31" s="60" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C31" s="89"/>
       <c r="D31" s="90" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E31" s="90" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="32" s="48" customFormat="1" ht="42.75" customHeight="1" spans="1:6">
       <c r="A32" s="88" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B32" s="60" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C32" s="89"/>
       <c r="D32" s="90" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E32" s="90" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="33" s="48" customFormat="1" ht="45.75" customHeight="1" spans="1:5">
       <c r="A33" s="88" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B33" s="60" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C33" s="89"/>
       <c r="D33" s="90" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E33" s="90" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="34" s="48" customFormat="1" ht="57" customHeight="1" spans="1:5">
       <c r="A34" s="88" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B34" s="60" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C34" s="89"/>
       <c r="D34" s="90" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E34" s="90" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="35" s="48" customFormat="1" ht="42.75" customHeight="1" spans="1:5">
       <c r="A35" s="88" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B35" s="60" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C35" s="89"/>
       <c r="D35" s="90" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E35" s="90" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="36" s="48" customFormat="1" ht="44.25" customHeight="1" spans="1:5">
       <c r="A36" s="88" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B36" s="60" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C36" s="89"/>
       <c r="D36" s="90" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E36" s="90" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="37" s="48" customFormat="1" ht="46.5" customHeight="1" spans="1:5">
       <c r="A37" s="88" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B37" s="60" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C37" s="89"/>
       <c r="D37" s="90" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E37" s="90" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="38" s="48" customFormat="1" ht="47.25" customHeight="1" spans="1:5">
       <c r="A38" s="88" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B38" s="60" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C38" s="89"/>
       <c r="D38" s="90" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E38" s="90" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="39" s="48" customFormat="1" ht="44.25" customHeight="1" spans="1:5">
       <c r="A39" s="88" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B39" s="60" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C39" s="89"/>
       <c r="D39" s="90" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E39" s="90" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="40" s="48" customFormat="1" ht="28.5" customHeight="1" spans="1:5">
       <c r="A40" s="88" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B40" s="60" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C40" s="89"/>
       <c r="D40" s="90" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E40" s="90" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="41" s="48" customFormat="1" ht="62.25" customHeight="1" spans="1:5">
       <c r="A41" s="88" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B41" s="60" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C41" s="89"/>
       <c r="D41" s="90" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E41" s="90" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="42" ht="29" spans="1:5">
       <c r="A42" s="88" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B42" s="60" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C42" s="60"/>
       <c r="D42" s="60" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E42" s="63" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -14045,30 +14055,30 @@
   <sheetData>
     <row r="1" ht="33.9" customHeight="1" spans="1:7">
       <c r="A1" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:7">
       <c r="A3" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>91</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:7">
@@ -14076,7 +14086,7 @@
         <v>70</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C4" s="6">
         <v>0.4</v>
@@ -14097,10 +14107,10 @@
     </row>
     <row r="5" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:7">
       <c r="A5" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C5" s="11">
         <v>0.4</v>
@@ -14121,10 +14131,10 @@
     </row>
     <row r="6" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:7">
       <c r="A6" s="14" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C6" s="11">
         <v>0.3</v>
@@ -14145,10 +14155,10 @@
     </row>
     <row r="7" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:7">
       <c r="A7" s="15" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C7" s="11">
         <v>0.3</v>
@@ -14169,10 +14179,10 @@
     </row>
     <row r="8" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:7">
       <c r="A8" s="16" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C8" s="11">
         <v>0.2</v>
@@ -14193,10 +14203,10 @@
     </row>
     <row r="9" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:7">
       <c r="A9" s="17" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C9" s="11">
         <v>0.5</v>
@@ -14217,10 +14227,10 @@
     </row>
     <row r="10" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:7">
       <c r="A10" s="18" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C10" s="11">
         <v>0.2</v>
@@ -14241,10 +14251,10 @@
     </row>
     <row r="11" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:7">
       <c r="A11" s="19" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C11" s="21">
         <v>0.2</v>
@@ -14318,17 +14328,17 @@
     </row>
     <row r="20" ht="20.25" customHeight="1" spans="1:8">
       <c r="A20" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:8">
       <c r="A22" s="37" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B22" s="38"/>
       <c r="C22" s="39"/>
       <c r="D22" s="37" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E22" s="38"/>
       <c r="F22" s="38"/>
@@ -14337,12 +14347,12 @@
     </row>
     <row r="23" ht="42.75" customHeight="1" spans="1:8">
       <c r="A23" s="40" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B23" s="41"/>
       <c r="C23" s="41"/>
       <c r="D23" s="41" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E23" s="41"/>
       <c r="F23" s="41"/>
@@ -14351,12 +14361,12 @@
     </row>
     <row r="24" ht="28.5" customHeight="1" spans="1:8">
       <c r="A24" s="40" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B24" s="41"/>
       <c r="C24" s="41"/>
       <c r="D24" s="42" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E24" s="42"/>
       <c r="F24" s="42"/>
@@ -14365,12 +14375,12 @@
     </row>
     <row r="25" ht="42.75" customHeight="1" spans="1:8">
       <c r="A25" s="40" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B25" s="41"/>
       <c r="C25" s="41"/>
       <c r="D25" s="42" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E25" s="42"/>
       <c r="F25" s="42"/>
@@ -14379,12 +14389,12 @@
     </row>
     <row r="26" ht="42.75" customHeight="1" spans="1:8">
       <c r="A26" s="40" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B26" s="41"/>
       <c r="C26" s="41"/>
       <c r="D26" s="42" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E26" s="42"/>
       <c r="F26" s="42"/>
@@ -14393,12 +14403,12 @@
     </row>
     <row r="27" ht="28.5" customHeight="1" spans="1:8">
       <c r="A27" s="40" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B27" s="41"/>
       <c r="C27" s="41"/>
       <c r="D27" s="41" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E27" s="41"/>
       <c r="F27" s="41"/>
@@ -14407,7 +14417,7 @@
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:8">
       <c r="A29" s="43" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B29" s="44"/>
       <c r="C29" s="44"/>
@@ -14419,11 +14429,11 @@
     </row>
     <row r="30" ht="30" customHeight="1" spans="1:8">
       <c r="A30" s="45" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B30" s="46"/>
       <c r="C30" s="41" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D30" s="41"/>
       <c r="E30" s="41"/>
@@ -14433,11 +14443,11 @@
     </row>
     <row r="31" ht="30" customHeight="1" spans="1:8">
       <c r="A31" s="45" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B31" s="46"/>
       <c r="C31" s="42" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D31" s="42"/>
       <c r="E31" s="42"/>
@@ -14447,11 +14457,11 @@
     </row>
     <row r="32" ht="30" customHeight="1" spans="1:8">
       <c r="A32" s="45" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B32" s="46"/>
       <c r="C32" s="42" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D32" s="42"/>
       <c r="E32" s="42"/>
@@ -14461,11 +14471,11 @@
     </row>
     <row r="33" ht="30" customHeight="1" spans="1:8">
       <c r="A33" s="45" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B33" s="46"/>
       <c r="C33" s="42" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D33" s="42"/>
       <c r="E33" s="42"/>
@@ -14479,7 +14489,7 @@
       </c>
       <c r="B34" s="46"/>
       <c r="C34" s="42" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D34" s="42"/>
       <c r="E34" s="42"/>
@@ -14489,11 +14499,11 @@
     </row>
     <row r="35" ht="30" customHeight="1" spans="1:8">
       <c r="A35" s="45" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B35" s="46"/>
       <c r="C35" s="41" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D35" s="41"/>
       <c r="E35" s="41"/>
